--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_217_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_217_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2434</v>
+        <v>5.1672</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1177</v>
+        <v>2.3103</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1257</v>
+        <v>2.8568</v>
       </c>
       <c r="G2" t="n">
         <v>4.5551</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.152</v>
+        <v>-0.2282</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1142</v>
+        <v>0.3068</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2662</v>
+        <v>-0.5351</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6589</v>
+        <v>2.5666</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4145</v>
+        <v>2.4085</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2444</v>
+        <v>0.1581</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5203</v>
+        <v>1.2688</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.07580000000000001</v>
+        <v>2.276</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5961</v>
+        <v>-1.0072</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6841</v>
+        <v>0.9109</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4937</v>
+        <v>0.9144</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1778</v>
+        <v>-0.0035</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.3579</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4179</v>
+        <v>1.3615</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4183</v>
+        <v>-1.0037</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4428</v>
+        <v>-0.9162</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0499</v>
+        <v>0.067</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6071</v>
+        <v>-0.9831</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>2.8223</v>
       </c>
       <c r="X3" t="n">
         <v>-1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8424</v>
+        <v>2.1768</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8187</v>
+        <v>0.6635</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0237</v>
+        <v>1.5133</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2688</v>
+        <v>1.5203</v>
       </c>
       <c r="H4" t="n">
-        <v>2.276</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0072</v>
+        <v>1.5961</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9109</v>
+        <v>0.6841</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9144</v>
+        <v>-0.4937</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0035</v>
+        <v>1.1778</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3579</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3615</v>
+        <v>0.4179</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0037</v>
+        <v>0.4183</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6403</v>
+        <v>-0.0393</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5228</v>
+        <v>0.2989</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1176</v>
+        <v>-0.3383</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8223</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>-1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.702</v>
+        <v>1.5715</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2175</v>
+        <v>-0.1925</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9195</v>
+        <v>1.764</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9896</v>
+        <v>0.7954</v>
       </c>
       <c r="H5" t="n">
-        <v>2.425</v>
+        <v>1.0229</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4354</v>
+        <v>-0.2275</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1243</v>
+        <v>0.1376</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8739</v>
+        <v>0.1008</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8653</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5511</v>
+        <v>0.9221</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6859</v>
+        <v>-0.2643</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2485</v>
+        <v>-0.4738</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0499</v>
+        <v>-0.3301</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1986</v>
+        <v>-0.1436</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3117</v>
+        <v>0.7246</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3851</v>
+        <v>1.8498</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6968</v>
+        <v>-1.1252</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7954</v>
+        <v>-1.4309</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0229</v>
+        <v>1.0349</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2275</v>
+        <v>-2.4658</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1376</v>
+        <v>1.1955</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1008</v>
+        <v>0.9747</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>0.2208</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6578000000000001</v>
+        <v>-2.6264</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9221</v>
+        <v>0.0602</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2643</v>
+        <v>-2.6866</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7336</v>
+        <v>0.1375</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5228</v>
+        <v>0.3501</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2109</v>
+        <v>-0.2126</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1418</v>
+        <v>0.3943</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
         <v>-0.1418</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6231</v>
+        <v>0.6657</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6139</v>
+        <v>-0.8505</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9908</v>
+        <v>1.5162</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4309</v>
+        <v>0.9896</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0349</v>
+        <v>2.425</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4658</v>
+        <v>-1.4354</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1955</v>
+        <v>0.1243</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9747</v>
+        <v>0.8739</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2208</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6264</v>
+        <v>0.8653</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0602</v>
+        <v>1.5511</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6866</v>
+        <v>-0.6859</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.036</v>
+        <v>0.2122</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1142</v>
+        <v>0.4169</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.2047</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3962</v>
+        <v>-0.7275</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1229</v>
+        <v>-0.9918</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2733</v>
+        <v>0.2644</v>
       </c>
       <c r="G8" t="n">
         <v>2.1593</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5474</v>
+        <v>0.2161</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6122</v>
+        <v>0.7433</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0649</v>
+        <v>-0.5272</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5288</v>
+        <v>-0.8883</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0794</v>
+        <v>-1.3717</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5506</v>
+        <v>0.4834</v>
       </c>
       <c r="G9" t="n">
         <v>0.3523</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9533</v>
+        <v>-0.3128</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>0.1849</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4305</v>
+        <v>-0.4977</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0943</v>
+        <v>-1.5046</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6332</v>
+        <v>-1.0434</v>
       </c>
       <c r="F10" t="n">
         <v>-0.4612</v>
@@ -1234,10 +1234,10 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4129</v>
+        <v>0.1768</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>-0.0077</v>
       </c>
       <c r="U10" t="n">
         <v>0.1845</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1071</v>
+        <v>-3.1235</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4983</v>
+        <v>-1.3804</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6087</v>
+        <v>-1.7432</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1381</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1133</v>
+        <v>-0.1298</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1142</v>
+        <v>0.2322</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2275</v>
+        <v>-0.362</v>
       </c>
       <c r="V11" t="n">
         <v>1.0722</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.2551</v>
+        <v>6.628500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0284</v>
+        <v>1.401799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>5.2267</v>
+        <v>5.2266</v>
       </c>
       <c r="G12" t="n">
-        <v>6.529600000000002</v>
+        <v>6.5296</v>
       </c>
       <c r="H12" t="n">
         <v>16.266</v>
@@ -1372,7 +1372,7 @@
         <v>1.8729</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.606199999999999</v>
+        <v>-3.6062</v>
       </c>
       <c r="N12" t="n">
         <v>8.003</v>
@@ -1390,16 +1390,16 @@
         <v>16.2366</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7307</v>
+        <v>-1.3575</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8887</v>
+        <v>2.2623</v>
       </c>
       <c r="U12" t="n">
         <v>-3.6198</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9356</v>
+        <v>4.935600000000001</v>
       </c>
       <c r="W12" t="n">
         <v>8.7194</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3184</v>
+        <v>4.4021</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9777</v>
+        <v>3.8598</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3407</v>
+        <v>0.5423</v>
       </c>
       <c r="G13" t="n">
         <v>1.366</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7204</v>
+        <v>0.8041</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1404</v>
+        <v>1.0225</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.42</v>
+        <v>-0.2183</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3994</v>
+        <v>2.4506</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5297</v>
+        <v>1.6357</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1303</v>
+        <v>0.8149</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4769</v>
+        <v>1.4923</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0051</v>
+        <v>0.3145</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4718</v>
+        <v>1.1778</v>
       </c>
       <c r="J14" t="n">
-        <v>0.989</v>
+        <v>1.2317</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0895</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1005</v>
+        <v>0.3914</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4659</v>
+        <v>0.2606</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0945</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3713</v>
+        <v>0.7863</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3454</v>
+        <v>0.7264</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2571</v>
+        <v>0.4916</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0883</v>
+        <v>0.2348</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
         <v>-1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0155</v>
+        <v>2.3879</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2035</v>
+        <v>2.3501</v>
       </c>
       <c r="F15" t="n">
-        <v>2.219</v>
+        <v>0.0378</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0563</v>
+        <v>-0.4769</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3891</v>
+        <v>-0.0051</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4454</v>
+        <v>-0.4718</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1243</v>
+        <v>0.989</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.4817</v>
+        <v>1.0895</v>
       </c>
       <c r="L15" t="n">
-        <v>1.606</v>
+        <v>-0.1005</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0679</v>
+        <v>-1.4659</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0926</v>
+        <v>-1.0945</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1605</v>
+        <v>-0.3713</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.7112</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2473</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2117</v>
+        <v>1.3339</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5637</v>
+        <v>1.0776</v>
       </c>
       <c r="U15" t="n">
-        <v>0.648</v>
+        <v>0.2563</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7886</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8197</v>
+        <v>0.2836</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7765</v>
+        <v>1.3396</v>
       </c>
       <c r="E16" t="n">
-        <v>0.928</v>
+        <v>1.6952</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8486</v>
+        <v>-0.3556</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4923</v>
+        <v>1.1283</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3145</v>
+        <v>-0.8726</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1778</v>
+        <v>2.0009</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2317</v>
+        <v>1.9507</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8401999999999999</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3914</v>
+        <v>1.9507</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2606</v>
+        <v>-0.8223</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.8726</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7863</v>
+        <v>0.0502</v>
       </c>
       <c r="P16" t="n">
         <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0523</v>
+        <v>-0.0206</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2161</v>
+        <v>-0.2555</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.2812</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5773</v>
+        <v>-1.501</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5908</v>
+        <v>1.7821</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1283</v>
+        <v>0.0563</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8726</v>
+        <v>-1.3891</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0009</v>
+        <v>1.4454</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9507</v>
+        <v>0.1243</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-1.4817</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9507</v>
+        <v>1.606</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8223</v>
+        <v>-0.0679</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8726</v>
+        <v>0.0926</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0502</v>
+        <v>-0.1605</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.7112</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>3.2473</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3738</v>
+        <v>1.4774</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3734</v>
+        <v>1.2663</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0004</v>
+        <v>0.2111</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1932</v>
+        <v>-0.9243</v>
       </c>
       <c r="E18" t="n">
         <v>1.3707</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5639</v>
+        <v>-2.295</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4762</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9489</v>
+        <v>-0.68</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1845</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7644</v>
+        <v>-0.4955</v>
       </c>
       <c r="V18" t="n">
         <v>0.5361</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5921</v>
+        <v>-1.2587</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0208</v>
+        <v>-1.457</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4286</v>
+        <v>0.1984</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6913</v>
+        <v>0.3345</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2965</v>
+        <v>0.0602</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3948</v>
+        <v>0.2742</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3383</v>
+        <v>1.3497</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7359</v>
+        <v>0.3361</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6022999999999999</v>
+        <v>1.0136</v>
       </c>
       <c r="M19" t="n">
-        <v>0.647</v>
+        <v>-1.0152</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4395</v>
+        <v>-0.2759</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2075</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0606</v>
+        <v>-1.1292</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2908</v>
+        <v>-0.2552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2302</v>
+        <v>-0.874</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7316</v>
+        <v>-1.3055</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6834</v>
+        <v>-2.6669</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0481</v>
+        <v>1.3614</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3</v>
+        <v>-0.6913</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.976</v>
+        <v>-0.2965</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6758999999999999</v>
+        <v>-0.3948</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1607</v>
+        <v>-1.3383</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7863</v>
+        <v>-0.7359</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6257</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1394</v>
+        <v>0.647</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1896</v>
+        <v>0.4395</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0502</v>
+        <v>0.2075</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8232</v>
+        <v>0.226</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5228</v>
+        <v>0.063</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3005</v>
+        <v>0.163</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0672</v>
+        <v>-1.6808</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1647</v>
+        <v>-0.5655</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0975</v>
+        <v>-1.1154</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3345</v>
+        <v>-0.3</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0602</v>
+        <v>-0.976</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2742</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3497</v>
+        <v>-0.1607</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3361</v>
+        <v>-0.7863</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0136</v>
+        <v>0.6257</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0152</v>
+        <v>-0.1394</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2759</v>
+        <v>-0.1896</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.0502</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9378</v>
+        <v>-0.7725</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.963</v>
+        <v>-0.4048</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9748</v>
+        <v>-0.3677</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1598</v>
+        <v>-1.7045</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8944</v>
+        <v>-2.3046</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7346</v>
+        <v>0.6001</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2509</v>
@@ -2170,13 +2170,13 @@
         <v>3.2473</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2328</v>
+        <v>0.6882</v>
       </c>
       <c r="T22" t="n">
-        <v>0.13</v>
+        <v>0.7198</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1028</v>
+        <v>-0.0316</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6778999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.585</v>
+        <v>-4.2305</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2456</v>
+        <v>-1.6558</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3395</v>
+        <v>-2.5747</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6443</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1004</v>
+        <v>-0.7459</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7468</v>
+        <v>-0.1571</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3536</v>
+        <v>-0.5889</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6083</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4225</v>
+        <v>-6.0123</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7893</v>
+        <v>-4.3791</v>
       </c>
       <c r="F24" t="n">
         <v>-1.6332</v>
@@ -2326,10 +2326,10 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4129</v>
+        <v>-0.1768</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8259</v>
+        <v>0.2361</v>
       </c>
       <c r="U24" t="n">
         <v>-0.4129</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.255200000000002</v>
+        <v>-6.255199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.618299999999998</v>
+        <v>-3.618399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6368</v>
+        <v>-2.6369</v>
       </c>
       <c r="G25" t="n">
         <v>-6.5296</v>
@@ -2404,10 +2404,10 @@
         <v>19.716</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7308</v>
+        <v>1.731</v>
       </c>
       <c r="T25" t="n">
-        <v>3.619699999999999</v>
+        <v>3.6198</v>
       </c>
       <c r="U25" t="n">
         <v>-1.8889</v>
